--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2234.52</v>
+        <v>2223.04</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21697.32</v>
+        <v>21470.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2359.09</v>
+        <v>2346.17</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2281.88</v>
+        <v>2269.38</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6080.46</v>
+        <v>6047.16</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3942.23</v>
+        <v>3937.22</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2481.84</v>
+        <v>2478.68</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10130.01</v>
+        <v>10166.16</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17754.66</v>
+        <v>17818.03</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2219.88</v>
+        <v>2244.02</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4975.66</v>
+        <v>5029.77</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1960.5</v>
+        <v>1966.95</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>838.23</v>
+        <v>842.13</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11088.14</v>
+        <v>11168.07</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10341.72</v>
+        <v>10323.38</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>31146.17</v>
+        <v>31090.93</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1374.44</v>
+        <v>1368.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2426.18</v>
+        <v>2438.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4366.88</v>
+        <v>4311.41</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5992.03</v>
+        <v>5915.91</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2838.35</v>
+        <v>2832.2</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7449.78</v>
+        <v>7433.66</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14734.15</v>
+        <v>14563.63</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1248.55</v>
+        <v>1234.1</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4146.81</v>
+        <v>4111.68</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25248.09</v>
+        <v>25034.22</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8353.639999999999</v>
+        <v>8346.92</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1818.38</v>
+        <v>1825.36</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2279.95</v>
+        <v>2288.7</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1272.92</v>
+        <v>1278.69</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6310.09</v>
+        <v>6326.82</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2034.28</v>
+        <v>2031.42</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3086.18</v>
+        <v>3090.13</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1486.01</v>
+        <v>1487.92</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2362.69</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2280.16</v>
+        <v>2308.18</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2095.71</v>
+        <v>2122.64</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6421.08</v>
+        <v>6503.59</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1417.23</v>
+        <v>1424.98</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>27710.23</v>
+        <v>27169.75</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7906.21</v>
+        <v>7792.89</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2277.46</v>
+        <v>2248.02</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>925.28</v>
+        <v>923.46</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2451.2</v>
+        <v>2451.21</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2426.48</v>
+        <v>2426.5</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2710.64</v>
+        <v>2714.4</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>794.7</v>
+        <v>791.97</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7857.41</v>
+        <v>7815.91</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1219.56</v>
+        <v>1235.98</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2185.7</v>
+        <v>2218.98</v>
       </c>
     </row>
     <row r="52">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5128.62</v>
+        <v>5253.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1376-54-CM26</t>
+          <t>681014-2-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>JUZGADO DE GARANTIA DE COPIAPO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2640.02</v>
+        <v>1893.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>681014-2-CM26</t>
+          <t>1376-54-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>JUZGADO DE GARANTIA DE COPIAPO</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1846.34</v>
+        <v>2706.76</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>39568.46</v>
+        <v>40768.29</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6771.66</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2932.22</v>
+        <v>2910.28</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>19071.93</v>
+        <v>18991.51</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1591.55</v>
+        <v>1595.92</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>842.04</v>
+        <v>844.36</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>44048.98</v>
+        <v>44355.65</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2422.59</v>
+        <v>2438.55</v>
       </c>
     </row>
     <row r="63">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5578.81</v>
+        <v>5615.55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1556-44-CM26</t>
+          <t>2175-16-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4065.61</v>
+        <v>7951.03</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2175-16-CM26</t>
+          <t>1556-44-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7880.83</v>
+        <v>4101.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5349-364-CM26</t>
+          <t>1028871-119-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4016.2</v>
+        <v>6923.64</v>
       </c>
     </row>
     <row r="67">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>71407.2</v>
+        <v>71333.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1028871-119-CM26</t>
+          <t>5349-364-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6930.79</v>
+        <v>4012.06</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6553.87</v>
+        <v>6544.23</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6027.63</v>
+        <v>5994.81</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5153.88</v>
+        <v>5125.81</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2793.38</v>
+        <v>2776.92</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2710.9</v>
+        <v>2694.92</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15438.43</v>
+        <v>15347.45</v>
       </c>
     </row>
     <row r="75">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>847.89</v>
+        <v>842.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2381-227-CM26</t>
+          <t>1171166-29-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1416.06</v>
+        <v>65249.04</v>
       </c>
     </row>
     <row r="77">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>55316.65</v>
+        <v>54980.52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1171166-29-CM26</t>
+          <t>2381-227-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>65647.94</v>
+        <v>1407.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1176812-13-CM26</t>
+          <t>1176812-18-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5488.05</v>
+        <v>2480.6</v>
       </c>
     </row>
     <row r="80">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>24451.24</v>
+        <v>24356.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1176812-18-CM26</t>
+          <t>1176812-13-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2490.21</v>
+        <v>5466.87</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>9926.92</v>
+        <v>9978.32</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4249.05</v>
+        <v>4436.69</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>11837.41</v>
+        <v>12181.24</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5574.03</v>
+        <v>5596.01</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2836.25</v>
+        <v>2882.99</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>75100.27</v>
+        <v>76338.03</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>10051.8</v>
+        <v>10217.47</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2154.06</v>
+        <v>2189.56</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>24177.35</v>
+        <v>24236.84</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1525.18</v>
+        <v>1505.54</v>
       </c>
     </row>
     <row r="92">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>30047.63</v>
+        <v>29660.79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4618-11-CM26</t>
+          <t>952751-37-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2401</v>
+        <v>1118.67</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4713-2-CM26</t>
+          <t>4618-11-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1094.38</v>
+        <v>2444.53</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>952751-37-CM26</t>
+          <t>4713-2-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1098.75</v>
+        <v>1114.22</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>879.5</v>
+        <v>893.28</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10245.65</v>
+        <v>10245.13</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11420.9</v>
+        <v>11420.32</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1415.27</v>
+        <v>1416.49</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>923.1</v>
+        <v>923.9</v>
       </c>
     </row>
     <row r="101">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>22705.86</v>
+        <v>22725.43</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1028871-192-CM26</t>
+          <t>1171166-94-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>14151.47</v>
+        <v>21422.01</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1171166-94-CM26</t>
+          <t>1028871-192-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>21333.88</v>
+        <v>14209.93</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2381-324-CM26</t>
+          <t>1028871-193-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1096.3</v>
+        <v>9501.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1077275-5-CM26</t>
+          <t>5349-550-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1859.89</v>
+        <v>4067.7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5349-550-CM26</t>
+          <t>2381-324-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4078.95</v>
+        <v>1093.28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1028871-193-CM26</t>
+          <t>1077275-5-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9528.190000000001</v>
+        <v>1854.76</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1502.06</v>
+        <v>1484.72</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1047.91</v>
+        <v>1035.81</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1441.77</v>
+        <v>1425.12</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12373.63</v>
+        <v>12230.79</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3294.98</v>
+        <v>3245.83</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3666.09</v>
+        <v>3645.04</v>
       </c>
     </row>
     <row r="114">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>45864.73</v>
+        <v>44797.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>751-107-CM26</t>
+          <t>778993-29-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5789.06</v>
+        <v>1940.25</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>778993-29-CM26</t>
+          <t>5349-624-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2004.15</v>
+        <v>765.92</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5349-624-CM26</t>
+          <t>751-107-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>791.15</v>
+        <v>5604.47</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1937.46</v>
+        <v>1902.33</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5465.03</v>
+        <v>5480.94</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5523.02</v>
+        <v>5569.89</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8949.08</v>
+        <v>8934.120000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4112.14</v>
+        <v>4162.75</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3304.93</v>
+        <v>3348.93</v>
       </c>
     </row>
     <row r="124">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>17932.18</v>
+        <v>18166.19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5350-862-CM26</t>
+          <t>1346283-80-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8037,17 +8037,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3140.61</v>
+        <v>1544.76</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1346283-80-CM26</t>
+          <t>5350-862-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1507.66</v>
+        <v>3217.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1558-132-CM26</t>
+          <t>1176812-49-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1491.27</v>
+        <v>3703.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1176812-49-CM26</t>
+          <t>1558-132-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3635.1</v>
+        <v>1519.47</v>
       </c>
     </row>
     <row r="129">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3151.25</v>
+        <v>3187.09</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1171166-140-CM26</t>
+          <t>2923-281-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6828.93</v>
+        <v>4025.86</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5350-873-CM26</t>
+          <t>1173453-23-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>77.419.860-1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>Centro de Educación y Trabajo CCP Copiapo</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>5190.08</v>
+        <v>3975.88</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1173453-23-CM26</t>
+          <t>5350-873-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>77.419.860-1</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP Copiapo</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3940.38</v>
+        <v>5236.83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2923-281-CM26</t>
+          <t>1171166-140-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3989.92</v>
+        <v>6890.44</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>6093.22</v>
+        <v>6112.39</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4146.44</v>
+        <v>4159.49</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2225.32</v>
+        <v>2229.93</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>30595.88</v>
+        <v>30456.02</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1747.95</v>
+        <v>1757.37</v>
       </c>
     </row>
     <row r="139">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6247.74</v>
+        <v>6281.38</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1554-816-CM26</t>
+          <t>1376-276-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2061.09</v>
+        <v>1688.33</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1376-276-CM26</t>
+          <t>1554-814-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1669.65</v>
+        <v>43557.44</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1554-814-CM26</t>
+          <t>1554-816-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>43075.69</v>
+        <v>2084.15</v>
       </c>
     </row>
     <row r="143">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4352.54</v>
+        <v>4385.51</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1171166-146-CM26</t>
+          <t>1197-52-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1448.84</v>
+        <v>2031.83</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1171166-147-CM26</t>
+          <t>1171166-155-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>13841.88</v>
+        <v>2449.98</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1171166-148-CM26</t>
+          <t>1171166-146-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.774.294-0</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6175.28</v>
+        <v>1459.63</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1171166-155-CM26</t>
+          <t>1171166-147-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2431.87</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1197-52-CM26</t>
+          <t>1171166-148-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2016.8</v>
+        <v>6221.28</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1079486-88-CM26</t>
+          <t>1079486-86-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1479.86</v>
+        <v>3964.41</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1079486-86-CM26</t>
+          <t>1079486-88-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3981.86</v>
+        <v>1473.37</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2381-600-CM26</t>
+          <t>2381-599-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3119.64</v>
+        <v>39419.33</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1557-166-CM26</t>
+          <t>2381-600-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2468.59</v>
+        <v>3085.7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2381-599-CM26</t>
+          <t>1557-166-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>39852.86</v>
+        <v>2441.74</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1331.8</v>
+        <v>1328.78</v>
       </c>
     </row>
     <row r="155">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1113.87</v>
+        <v>1111.34</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2172-12-CM26</t>
+          <t>952751-128-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1113.91</v>
+        <v>5127.42</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>952751-128-CM26</t>
+          <t>2172-12-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5102.36</v>
+        <v>1119.38</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1433.12</v>
+        <v>1437.88</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2156.25</v>
+        <v>2163.41</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1628.04</v>
+        <v>1633.22</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3884.61</v>
+        <v>3905.26</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5158.27</v>
+        <v>5245.51</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4789.98</v>
+        <v>4838.7</v>
       </c>
     </row>
     <row r="164">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>4104.74</v>
+        <v>4073.6</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2923-435-CM26</t>
+          <t>1171166-173-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1964.44</v>
+        <v>1227.56</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1171166-173-CM26</t>
+          <t>1558-200-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1248.65</v>
+        <v>2656.82</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1558-200-CM26</t>
+          <t>2923-435-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2702.48</v>
+        <v>1931.25</v>
       </c>
     </row>
     <row r="168">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2284.06</v>
+        <v>2251.64</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>904-71-CM26</t>
+          <t>3281-49-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1925.85</v>
+        <v>2166.87</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5349-1166-CM26</t>
+          <t>904-71-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>4108.3</v>
+        <v>1899.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3281-49-CM26</t>
+          <t>5349-1166-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2197.06</v>
+        <v>4051.85</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>42751.32</v>
+        <v>42486.27</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2102.1</v>
+        <v>2133.4</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3410.87</v>
+        <v>3461.66</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1172.96</v>
+        <v>1190.43</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1748.65</v>
+        <v>1788.08</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>845</v>
+        <v>864.0599999999999</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2093.4</v>
+        <v>2107.86</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4564.28</v>
+        <v>4595.79</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2751.36</v>
+        <v>2770.36</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2831.49</v>
+        <v>2840.24</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>8221.02</v>
+        <v>8199.280000000001</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>840.86</v>
+        <v>838.64</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>40045.26</v>
+        <v>39511.85</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1237.31</v>
+        <v>1218.98</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1318.29</v>
+        <v>1298.76</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1327.98</v>
+        <v>1308.3</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>15220.8</v>
+        <v>15365.38</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3062.45</v>
+        <v>3074.4</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>807.42</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1054.49</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4196.71</v>
+        <v>4213.04</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1984.07</v>
+        <v>1988.62</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2340.71</v>
+        <v>2356.37</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1988.04</v>
+        <v>2001.95</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>7913</v>
+        <v>7897.14</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1605.18</v>
+        <v>1595.89</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>6057.49</v>
+        <v>6022.43</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4057.79</v>
+        <v>4034.3</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5624.68</v>
+        <v>5533.91</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3838.54</v>
+        <v>3817.26</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>877.37</v>
+        <v>873.0599999999999</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,190 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3415.48</v>
+        <v>3438.34</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1554-1236-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Barron Vieyra International Ltda.</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>2202.39</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1554-1444-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>9811.629999999999</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2859-908-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>1331.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2037,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2358,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2423,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2984,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3244,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3691,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3756,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4207,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4646,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4837,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4902,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5097,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5223,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5414,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5540,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5605,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5670,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5861,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5926,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6117,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6369,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6499,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6564,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6755,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6820,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7068,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7133,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7324,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7389,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7454,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7519,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7584,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7836,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7966,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8092,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8157,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8222,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8287,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8352,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8417,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8482,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8608,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8738,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8803,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8868,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8933,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9315,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9380,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9445,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9510,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9697,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9762,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9888,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9953,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10018,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10083,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10274,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10461,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10587,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10717,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10782,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10847,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10977,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11042,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11107,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11172,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11237,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11367,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11615,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11680,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11745,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11875,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12001,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12066,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12444,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12509,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12574,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12700,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12765,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12891,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13021,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13086,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13151,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13216,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13281,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13537,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13602,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13732,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13797,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13862,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13992,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14057,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14122,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14248,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14374,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14565,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14630,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14695,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14760,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14890,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14955,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15020,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15150,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15215,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15280,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15410,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15540,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15792,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15922,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16117,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16182,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16247,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16312,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16377,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16442,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16572,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16637,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16702,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16767,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16893,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16958,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17023,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17088,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17214,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17279,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17657,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17913,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18108,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18173,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18238,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18303,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18368,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18433,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18498,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18563,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18628,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18693,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18758,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18823,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18888,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18953,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19018,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19083,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19148,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19274,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19339,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19404,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19469,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19534,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19599,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19725,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19790,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19855,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19920,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20050,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20115,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20245,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20310,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20375,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20440,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20505,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20635,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20700,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20830,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20960,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21090,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21216,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21281,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21346,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21411,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21606,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21732,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21797,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21862,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22122,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22187,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22382,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22447,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22512,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22577,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22642,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23032,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23292,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23418,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23548,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23613,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23743,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23808,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23873,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
@@ -1720,7 +1720,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2297,7 +2301,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2549,7 +2557,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2610,7 +2622,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2862,7 +2878,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8547,7 +8567,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9254,7 +9278,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9575,7 +9603,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10400,7 +10432,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10526,7 +10562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14187,7 +14227,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16832,7 +16876,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17153,7 +17201,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21671,7 +21723,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M365"/>
+  <dimension ref="A1:M385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12566,7 +12566,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>411-56-CM26</t>
+          <t>411-57-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12606,32 +12606,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1595.92</v>
+        <v>844.36</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>411-57-CM26</t>
+          <t>411-56-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12671,22 +12667,26 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>844.36</v>
+        <v>1595.92</v>
       </c>
     </row>
     <row r="192">
@@ -12883,7 +12883,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2175-16-CM26</t>
+          <t>1556-44-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12903,17 +12903,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12942,13 +12942,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7951.03</v>
+        <v>4101.82</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1556-44-CM26</t>
+          <t>2175-16-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12968,17 +12968,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13007,13 +13007,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4101.82</v>
+        <v>7951.03</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5349-364-CM26</t>
+          <t>1028871-119-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13053,17 +13053,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4012.06</v>
+        <v>6923.64</v>
       </c>
     </row>
     <row r="198">
@@ -13143,7 +13143,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1028871-119-CM26</t>
+          <t>5349-364-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13183,17 +13183,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13202,7 +13202,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6923.64</v>
+        <v>4012.06</v>
       </c>
     </row>
     <row r="200">
@@ -13273,7 +13273,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1176812-7-CM26</t>
+          <t>1554-272-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13298,12 +13298,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13313,32 +13313,28 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>5994.81</v>
+        <v>5125.81</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1554-272-CM26</t>
+          <t>1176812-7-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13363,12 +13359,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13378,28 +13374,32 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5125.81</v>
+        <v>5994.81</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1176812-10-CM26</t>
+          <t>1176812-15-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13458,13 +13458,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2694.92</v>
+        <v>15347.45</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1176812-15-CM26</t>
+          <t>1176812-10-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>15347.45</v>
+        <v>2694.92</v>
       </c>
     </row>
     <row r="205">
@@ -13594,7 +13594,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1171166-29-CM26</t>
+          <t>2381-227-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13619,12 +13619,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13634,17 +13634,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>65249.04</v>
+        <v>1407.45</v>
       </c>
     </row>
     <row r="207">
@@ -13724,7 +13724,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2381-227-CM26</t>
+          <t>1171166-29-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13764,17 +13764,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13783,13 +13783,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1407.45</v>
+        <v>65249.04</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1176812-13-CM26</t>
+          <t>2381-233-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13814,12 +13814,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13829,17 +13829,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5466.87</v>
+        <v>24356.87</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2381-233-CM26</t>
+          <t>1176812-18-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13894,17 +13894,17 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13913,13 +13913,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>24356.87</v>
+        <v>2480.6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1176812-18-CM26</t>
+          <t>1176812-13-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13959,17 +13959,17 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2480.6</v>
+        <v>5466.87</v>
       </c>
     </row>
     <row r="212">
@@ -14179,7 +14179,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1376-124-CM26</t>
+          <t>1554-298-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14219,32 +14219,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2189.56</v>
+        <v>2882.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1171166-67-CM26</t>
+          <t>1376-124-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14269,12 +14265,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14284,17 +14280,17 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14303,13 +14299,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>10217.47</v>
+        <v>2189.56</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1554-298-CM26</t>
+          <t>2380-376-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14329,17 +14325,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14349,28 +14345,32 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2882.99</v>
+        <v>76338.03</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2380-376-CM26</t>
+          <t>1171166-67-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14410,17 +14410,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14429,13 +14429,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>76338.03</v>
+        <v>10217.47</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1556-67-CM26</t>
+          <t>1554-336-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14475,32 +14475,28 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1505.54</v>
+        <v>29660.79</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1554-336-CM26</t>
+          <t>1556-67-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14525,12 +14521,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14540,28 +14536,32 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>29660.79</v>
+        <v>1505.54</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4713-2-CM26</t>
+          <t>4618-11-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14601,17 +14601,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14620,13 +14620,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1114.22</v>
+        <v>2444.53</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4618-11-CM26</t>
+          <t>4713-2-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2444.53</v>
+        <v>1114.22</v>
       </c>
     </row>
     <row r="223">
@@ -14756,7 +14756,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1171166-80-CM26</t>
+          <t>1171166-78-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14815,13 +14815,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>11420.32</v>
+        <v>10245.13</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1171166-78-CM26</t>
+          <t>1171166-80-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14880,13 +14880,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>10245.13</v>
+        <v>11420.32</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1133261-32-CM26</t>
+          <t>1176812-33-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14945,13 +14945,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>923.9</v>
+        <v>1416.49</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1171166-83-CM26</t>
+          <t>1133261-32-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15010,13 +15010,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>22725.43</v>
+        <v>923.9</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1176812-33-CM26</t>
+          <t>1171166-83-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1416.49</v>
+        <v>22725.43</v>
       </c>
     </row>
     <row r="229">
@@ -15471,7 +15471,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1171166-102-CM26</t>
+          <t>1171166-105-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15511,17 +15511,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15530,13 +15530,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1484.72</v>
+        <v>12230.79</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1171166-105-CM26</t>
+          <t>1171166-102-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15576,17 +15576,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>12230.79</v>
+        <v>1484.72</v>
       </c>
     </row>
     <row r="237">
@@ -15788,7 +15788,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>778993-29-CM26</t>
+          <t>5349-624-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15813,12 +15813,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15828,17 +15828,17 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -15847,13 +15847,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1940.25</v>
+        <v>765.92</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5349-624-CM26</t>
+          <t>778993-29-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15878,12 +15878,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15893,17 +15893,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>765.92</v>
+        <v>1940.25</v>
       </c>
     </row>
     <row r="242">
@@ -16373,7 +16373,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5350-862-CM26</t>
+          <t>1346283-80-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16393,17 +16393,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16413,17 +16413,17 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16432,13 +16432,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3217.9</v>
+        <v>1544.76</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1346283-80-CM26</t>
+          <t>5350-862-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16458,17 +16458,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16478,17 +16478,17 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16497,7 +16497,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1544.76</v>
+        <v>3217.9</v>
       </c>
     </row>
     <row r="251">
@@ -16763,7 +16763,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5350-873-CM26</t>
+          <t>1173453-23-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16788,12 +16788,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>77.419.860-1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16803,17 +16803,17 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16822,13 +16822,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>5236.83</v>
+        <v>3975.88</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1173453-23-CM26</t>
+          <t>2923-281-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16848,17 +16848,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.419.860-1</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16887,13 +16887,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3975.88</v>
+        <v>4025.86</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2923-281-CM26</t>
+          <t>5350-873-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16913,17 +16913,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16933,17 +16933,17 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4025.86</v>
+        <v>5236.83</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1557-128-CM26</t>
+          <t>1171166-142-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16983,12 +16983,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16998,17 +16998,17 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -17017,13 +17017,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4159.49</v>
+        <v>6112.39</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1171166-142-CM26</t>
+          <t>1557-128-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17048,12 +17048,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17063,17 +17063,17 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -17082,7 +17082,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6112.39</v>
+        <v>4159.49</v>
       </c>
     </row>
     <row r="260">
@@ -17218,7 +17218,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2322-277-CM26</t>
+          <t>2322-278-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17277,13 +17277,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1757.37</v>
+        <v>6281.38</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2322-278-CM26</t>
+          <t>2322-277-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17342,13 +17342,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>6281.38</v>
+        <v>1757.37</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1376-276-CM26</t>
+          <t>1554-816-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17373,12 +17373,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17403,7 +17403,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1688.33</v>
+        <v>2084.15</v>
       </c>
     </row>
     <row r="265">
@@ -17470,7 +17470,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1554-816-CM26</t>
+          <t>1376-276-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17495,12 +17495,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2084.15</v>
+        <v>1688.33</v>
       </c>
     </row>
     <row r="267">
@@ -17596,7 +17596,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1171166-148-CM26</t>
+          <t>1197-52-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17621,12 +17621,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17655,13 +17655,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>6221.28</v>
+        <v>2031.83</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1171166-155-CM26</t>
+          <t>1171166-146-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17701,32 +17701,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2449.98</v>
+        <v>1459.63</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1171166-146-CM26</t>
+          <t>1171166-147-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17746,7 +17742,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17766,28 +17762,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1459.63</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1171166-147-CM26</t>
+          <t>1171166-148-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17827,17 +17827,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17846,13 +17846,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>13945</v>
+        <v>6221.28</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1197-52-CM26</t>
+          <t>1171166-155-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17877,12 +17877,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17892,17 +17892,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17911,13 +17911,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2031.83</v>
+        <v>2449.98</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1079486-88-CM26</t>
+          <t>1079486-86-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17957,17 +17957,17 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -17976,13 +17976,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1473.37</v>
+        <v>3964.41</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1079486-86-CM26</t>
+          <t>1079486-88-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18022,17 +18022,17 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3964.41</v>
+        <v>1473.37</v>
       </c>
     </row>
     <row r="275">
@@ -18112,7 +18112,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2381-600-CM26</t>
+          <t>1557-166-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18137,12 +18137,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3085.7</v>
+        <v>2441.74</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1557-166-CM26</t>
+          <t>2381-600-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18236,7 +18236,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2441.74</v>
+        <v>3085.7</v>
       </c>
     </row>
     <row r="278">
@@ -19278,7 +19278,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1171166-204-CM26</t>
+          <t>4357-167-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19298,17 +19298,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19337,13 +19337,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3461.66</v>
+        <v>1190.43</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4357-167-CM26</t>
+          <t>1171166-204-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19363,17 +19363,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19402,7 +19402,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1190.43</v>
+        <v>3461.66</v>
       </c>
     </row>
     <row r="296">
@@ -19473,7 +19473,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1557-220-CM26</t>
+          <t>5349-1205-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19498,12 +19498,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19513,17 +19513,17 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -19532,13 +19532,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1788.08</v>
+        <v>864.0599999999999</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5349-1205-CM26</t>
+          <t>1557-220-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19563,12 +19563,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19578,17 +19578,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>864.0599999999999</v>
+        <v>1788.08</v>
       </c>
     </row>
     <row r="299">
@@ -19989,7 +19989,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5349-1293-CM26</t>
+          <t>4357-180-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20009,17 +20009,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20029,17 +20029,17 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.556.184-1</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -20048,13 +20048,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1308.3</v>
+        <v>1298.76</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3332-77-CM26</t>
+          <t>5349-1293-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20074,17 +20074,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20094,17 +20094,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20113,13 +20113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1218.98</v>
+        <v>1308.3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>4357-180-CM26</t>
+          <t>3332-77-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20144,12 +20144,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20159,17 +20159,17 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>GRUPO DK SERVICIOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.556.184-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1298.76</v>
+        <v>1218.98</v>
       </c>
     </row>
     <row r="308">
@@ -20704,7 +20704,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5350-1184-CM26</t>
+          <t>1171166-217-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20724,17 +20724,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20744,17 +20744,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20763,13 +20763,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6022.43</v>
+        <v>1595.89</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1171166-217-CM26</t>
+          <t>2381-872-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20809,17 +20809,17 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -20828,13 +20828,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1595.89</v>
+        <v>4034.3</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2381-872-CM26</t>
+          <t>5350-1184-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20854,17 +20854,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>4034.3</v>
+        <v>6022.43</v>
       </c>
     </row>
     <row r="319">
@@ -21545,7 +21545,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1171166-215-CM26</t>
+          <t>4357-253-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21604,13 +21604,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>7919.28</v>
+        <v>1772.21</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4357-253-CM26</t>
+          <t>1171166-215-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21630,17 +21630,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1772.21</v>
+        <v>7919.28</v>
       </c>
     </row>
     <row r="331">
@@ -21805,7 +21805,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1554-1392-CM26</t>
+          <t>2381-998-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21830,12 +21830,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21845,12 +21845,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -21864,13 +21864,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>859.45</v>
+        <v>1469.65</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2381-998-CM26</t>
+          <t>1554-1392-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21895,12 +21895,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21910,12 +21910,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -21929,13 +21929,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1469.65</v>
+        <v>859.45</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1554-1444-CM26</t>
+          <t>5349-1700-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21960,12 +21960,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21975,17 +21975,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -21994,13 +21994,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>9811.629999999999</v>
+        <v>2260.84</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5349-1700-CM26</t>
+          <t>1554-1444-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22025,12 +22025,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22040,17 +22040,17 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -22059,7 +22059,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2260.84</v>
+        <v>9811.629999999999</v>
       </c>
     </row>
     <row r="337">
@@ -22325,7 +22325,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1376-668-CM26</t>
+          <t>1079486-207-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22350,12 +22350,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22365,17 +22365,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1074.6</v>
+        <v>2857.34</v>
       </c>
     </row>
     <row r="342">
@@ -22455,7 +22455,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1079486-207-CM26</t>
+          <t>1376-668-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22480,12 +22480,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22495,17 +22495,17 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -22514,7 +22514,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2857.34</v>
+        <v>1074.6</v>
       </c>
     </row>
     <row r="344">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -22650,7 +22650,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5349-1893-CM26</t>
+          <t>5349-1854-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22665,12 +22665,12 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -22690,17 +22690,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22709,13 +22709,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>3823.98</v>
+        <v>1515.65</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2381-1225-CM26</t>
+          <t>5349-1893-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -22740,12 +22740,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>16366.97</v>
+        <v>3823.98</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2175-336-CM26</t>
+          <t>2381-1225-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22800,17 +22800,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22839,13 +22839,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1009.39</v>
+        <v>16366.97</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1554-1578-CM26</t>
+          <t>2175-336-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22870,12 +22870,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22885,17 +22885,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -22904,13 +22904,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>9030.950000000001</v>
+        <v>1009.39</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1176812-85-CM26</t>
+          <t>1554-1578-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -22935,12 +22935,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1085.05</v>
+        <v>9030.950000000001</v>
       </c>
     </row>
     <row r="351">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -23170,7 +23170,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>681007-34-CM26</t>
+          <t>1176812-85-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23190,17 +23190,17 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23229,13 +23229,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>770.42</v>
+        <v>1085.05</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3703-527-CM26</t>
+          <t>681007-34-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23255,17 +23255,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23294,13 +23294,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1570.42</v>
+        <v>770.42</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5350-1506-CM26</t>
+          <t>3703-527-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23315,22 +23315,22 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23340,17 +23340,17 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -23359,13 +23359,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>5880.84</v>
+        <v>1570.42</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2859-1082-CM26</t>
+          <t>5350-1506-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23390,12 +23390,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23405,28 +23405,32 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2079.68</v>
+        <v>5880.84</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1557-335-CM26</t>
+          <t>2859-1082-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23451,12 +23455,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23466,32 +23470,28 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3220.19</v>
+        <v>2079.68</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2380-1711-CM26</t>
+          <t>1557-335-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23516,12 +23516,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23531,17 +23531,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23550,13 +23550,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>842.33</v>
+        <v>3220.19</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1171166-234-CM26</t>
+          <t>2380-1711-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23571,7 +23571,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -23581,12 +23581,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23615,7 +23615,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1162.18</v>
+        <v>842.33</v>
       </c>
     </row>
     <row r="361">
@@ -23686,7 +23686,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1346283-254-CM26</t>
+          <t>1171166-234-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23701,22 +23701,22 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2932.42</v>
+        <v>1162.18</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1346283-255-CM26</t>
+          <t>1346283-250-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2766.91</v>
+        <v>1753.99</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1346283-250-CM26</t>
+          <t>1346283-254-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1753.99</v>
+        <v>2932.42</v>
       </c>
     </row>
     <row r="365">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -23941,6 +23941,1298 @@
       </c>
       <c r="M365" s="2" t="n">
         <v>763.26</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1346283-255-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>2766.91</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1171166-236-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>2085.16</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>5349-2001-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>1937.09</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1171166-231-CM26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>RUSTIC PINK SPA</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>77.649.678-2</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>1121.57</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2859-1220-CM26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>1021.59</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1171166-239-CM26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>2404.85</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1176812-92-CM26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>1271.92</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1171166-232-CM26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>1745.52</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1176812-91-CM26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>1182.52</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1171166-222-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>3520.47</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>5349-2075-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>3759.66</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1557-369-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>4097.57</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1557-370-CM26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
+        <v>1873.47</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>4357-323-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>69.030.600-k</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>1497.32</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1176812-99-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>1910.4</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>411-472-CM26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="n">
+        <v>758.79</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1554-1757-CM26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA MANZANO S A</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="n">
+        <v>27067.27</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>5349-2109-CM26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="n">
+        <v>786.63</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>681006-36-CM26</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="n">
+        <v>744.92</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1557-376-CM26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>1378.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M385"/>
+  <dimension ref="A1:M386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12948,7 +12948,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2175-16-CM26</t>
+          <t>1556-44-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12968,17 +12968,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13007,13 +13007,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>7951.03</v>
+        <v>4101.82</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1556-44-CM26</t>
+          <t>2175-16-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13053,12 +13053,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4101.82</v>
+        <v>7951.03</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1028871-117-CM26</t>
+          <t>1028871-119-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13137,13 +13137,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>71333.55</v>
+        <v>6923.64</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5349-364-CM26</t>
+          <t>1028871-117-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13183,17 +13183,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13202,13 +13202,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4012.06</v>
+        <v>71333.55</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1028871-119-CM26</t>
+          <t>5349-364-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13233,12 +13233,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13248,17 +13248,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>6923.64</v>
+        <v>4012.06</v>
       </c>
     </row>
     <row r="201">
@@ -13464,7 +13464,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1176812-8-CM26</t>
+          <t>1176812-15-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13504,17 +13504,17 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2776.92</v>
+        <v>15347.45</v>
       </c>
     </row>
     <row r="205">
@@ -13594,7 +13594,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1176812-15-CM26</t>
+          <t>1176812-8-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13634,17 +13634,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13653,13 +13653,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>15347.45</v>
+        <v>2776.92</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2381-227-CM26</t>
+          <t>1171166-29-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13684,12 +13684,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13699,17 +13699,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13718,13 +13718,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1407.45</v>
+        <v>65249.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1171166-29-CM26</t>
+          <t>2381-227-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13764,17 +13764,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>65249.04</v>
+        <v>1407.45</v>
       </c>
     </row>
     <row r="209">
@@ -13854,7 +13854,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1176812-13-CM26</t>
+          <t>1176812-18-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13894,17 +13894,17 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13913,13 +13913,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5466.87</v>
+        <v>2480.6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2381-233-CM26</t>
+          <t>1176812-13-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13959,17 +13959,17 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13978,13 +13978,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>24356.87</v>
+        <v>5466.87</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1176812-18-CM26</t>
+          <t>2381-233-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14009,12 +14009,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14024,17 +14024,17 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -14043,7 +14043,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2480.6</v>
+        <v>24356.87</v>
       </c>
     </row>
     <row r="213">
@@ -14244,7 +14244,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1554-298-CM26</t>
+          <t>2380-376-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14264,17 +14264,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14284,22 +14284,26 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2882.99</v>
+        <v>76338.03</v>
       </c>
     </row>
     <row r="217">
@@ -14370,7 +14374,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2380-376-CM26</t>
+          <t>1171166-67-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14390,17 +14394,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14410,17 +14414,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14429,13 +14433,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>76338.03</v>
+        <v>10217.47</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1171166-67-CM26</t>
+          <t>1554-298-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14460,12 +14464,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14475,32 +14479,28 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>10217.47</v>
+        <v>2882.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1556-67-CM26</t>
+          <t>1554-336-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14525,12 +14525,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14540,32 +14540,28 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA MANZANO S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.908.760-k</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1505.54</v>
+        <v>29660.79</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1554-336-CM26</t>
+          <t>1556-67-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14590,12 +14586,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14605,22 +14601,26 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MANZANO S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.908.760-k</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>29660.79</v>
+        <v>1505.54</v>
       </c>
     </row>
     <row r="222">
@@ -14951,7 +14951,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1171166-83-CM26</t>
+          <t>1176812-33-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15010,13 +15010,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>22725.43</v>
+        <v>1416.49</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1176812-33-CM26</t>
+          <t>1133261-32-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15075,13 +15075,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1416.49</v>
+        <v>923.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1133261-32-CM26</t>
+          <t>1171166-83-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>923.9</v>
+        <v>22725.43</v>
       </c>
     </row>
     <row r="230">
@@ -15276,7 +15276,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2381-324-CM26</t>
+          <t>1077275-5-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15316,17 +15316,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1093.28</v>
+        <v>1854.76</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1077275-5-CM26</t>
+          <t>2381-324-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15381,17 +15381,17 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1854.76</v>
+        <v>1093.28</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5349-550-CM26</t>
+          <t>1028871-193-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15446,17 +15446,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>4067.7</v>
+        <v>9501.9</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1028871-193-CM26</t>
+          <t>5349-550-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15496,12 +15496,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15511,17 +15511,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15530,13 +15530,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>9501.9</v>
+        <v>4067.7</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1171166-102-CM26</t>
+          <t>1171166-105-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15576,17 +15576,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15595,13 +15595,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1484.72</v>
+        <v>12230.79</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1171166-105-CM26</t>
+          <t>1171166-102-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15641,17 +15641,17 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -15660,7 +15660,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12230.79</v>
+        <v>1484.72</v>
       </c>
     </row>
     <row r="238">
@@ -15853,7 +15853,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>751-107-CM26</t>
+          <t>778993-29-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15878,12 +15878,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.946.100-2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15893,17 +15893,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15912,13 +15912,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>5604.47</v>
+        <v>1940.25</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5349-624-CM26</t>
+          <t>751-107-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15943,12 +15943,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15958,17 +15958,17 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15977,13 +15977,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>765.92</v>
+        <v>5604.47</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>778993-29-CM26</t>
+          <t>5349-624-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.946.100-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16042,7 +16042,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1940.25</v>
+        <v>765.92</v>
       </c>
     </row>
     <row r="244">
@@ -16763,7 +16763,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5350-873-CM26</t>
+          <t>1171166-140-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16783,17 +16783,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16803,17 +16803,17 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16822,13 +16822,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>5236.83</v>
+        <v>6890.44</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1173453-23-CM26</t>
+          <t>5350-873-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16853,12 +16853,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.419.860-1</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16868,17 +16868,17 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16887,13 +16887,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>3975.88</v>
+        <v>5236.83</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2923-281-CM26</t>
+          <t>1173453-23-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16913,17 +16913,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>77.419.860-1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16933,12 +16933,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4025.86</v>
+        <v>3975.88</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1171166-140-CM26</t>
+          <t>2923-281-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16983,12 +16983,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16998,12 +16998,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6890.44</v>
+        <v>4025.86</v>
       </c>
     </row>
     <row r="259">
@@ -17474,7 +17474,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1554-814-CM26</t>
+          <t>1376-276-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17499,12 +17499,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17529,13 +17529,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>43557.44</v>
+        <v>1688.33</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1376-276-CM26</t>
+          <t>1554-814-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17560,12 +17560,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17590,7 +17590,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1688.33</v>
+        <v>43557.44</v>
       </c>
     </row>
     <row r="268">
@@ -17661,7 +17661,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1197-52-CM26</t>
+          <t>1171166-146-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17681,17 +17681,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17701,32 +17701,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2031.83</v>
+        <v>1459.63</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1171166-146-CM26</t>
+          <t>1171166-147-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17746,7 +17742,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17766,28 +17762,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1459.63</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1171166-147-CM26</t>
+          <t>1171166-148-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17827,17 +17827,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17846,13 +17846,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>13945</v>
+        <v>6221.28</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1171166-148-CM26</t>
+          <t>1171166-155-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17892,17 +17892,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17911,13 +17911,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>6221.28</v>
+        <v>2449.98</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1171166-155-CM26</t>
+          <t>1197-52-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17942,12 +17942,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17957,17 +17957,17 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2449.98</v>
+        <v>2031.83</v>
       </c>
     </row>
     <row r="274">
@@ -18177,7 +18177,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1557-166-CM26</t>
+          <t>2381-600-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18236,13 +18236,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2441.74</v>
+        <v>3085.7</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2381-600-CM26</t>
+          <t>1557-166-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18267,12 +18267,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18301,7 +18301,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3085.7</v>
+        <v>2441.74</v>
       </c>
     </row>
     <row r="279">
@@ -19087,7 +19087,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>904-71-CM26</t>
+          <t>3281-49-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19146,13 +19146,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1899.39</v>
+        <v>2166.87</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3281-49-CM26</t>
+          <t>5349-1166-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19192,17 +19192,17 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -19211,13 +19211,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2166.87</v>
+        <v>4051.85</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5349-1166-CM26</t>
+          <t>904-71-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19242,12 +19242,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19257,17 +19257,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -19276,7 +19276,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4051.85</v>
+        <v>1899.39</v>
       </c>
     </row>
     <row r="294">
@@ -19343,7 +19343,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4357-167-CM26</t>
+          <t>1171166-204-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19363,17 +19363,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19402,13 +19402,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1190.43</v>
+        <v>3461.66</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1171166-204-CM26</t>
+          <t>4357-167-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19428,17 +19428,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19467,7 +19467,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3461.66</v>
+        <v>1190.43</v>
       </c>
     </row>
     <row r="297">
@@ -20054,7 +20054,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3332-77-CM26</t>
+          <t>5349-1293-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20074,17 +20074,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20094,17 +20094,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20113,13 +20113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1218.98</v>
+        <v>1308.3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5349-1293-CM26</t>
+          <t>3332-77-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20139,17 +20139,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20159,17 +20159,17 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -20178,7 +20178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1308.3</v>
+        <v>1218.98</v>
       </c>
     </row>
     <row r="308">
@@ -20314,7 +20314,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>411-306-CM26</t>
+          <t>5349-1370-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20334,17 +20334,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20354,17 +20354,17 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -20373,13 +20373,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1058.59</v>
+        <v>4213.04</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5349-1370-CM26</t>
+          <t>411-306-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20399,17 +20399,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20419,17 +20419,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20438,7 +20438,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>4213.04</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="312">
@@ -20704,7 +20704,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5350-1184-CM26</t>
+          <t>1171166-217-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20724,17 +20724,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20744,17 +20744,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20763,13 +20763,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6022.43</v>
+        <v>1595.89</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2381-872-CM26</t>
+          <t>5350-1184-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20789,17 +20789,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20828,13 +20828,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>4034.3</v>
+        <v>6022.43</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1171166-217-CM26</t>
+          <t>2381-872-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20859,12 +20859,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20874,17 +20874,17 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -20893,7 +20893,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1595.89</v>
+        <v>4034.3</v>
       </c>
     </row>
     <row r="319">
@@ -21350,7 +21350,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5349-1628-CM26</t>
+          <t>4355-719-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21375,12 +21375,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21390,17 +21390,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21409,13 +21409,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>4131.42</v>
+        <v>4572.16</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>4355-719-CM26</t>
+          <t>2381-974-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21440,12 +21440,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21455,12 +21455,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -21474,13 +21474,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4572.16</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2381-974-CM26</t>
+          <t>5349-1628-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21505,12 +21505,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21520,17 +21520,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6415</v>
+        <v>4131.42</v>
       </c>
     </row>
     <row r="329">
@@ -21675,7 +21675,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1376-564-CM26</t>
+          <t>1376-565-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21715,17 +21715,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21734,13 +21734,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3158.7</v>
+        <v>2337.71</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1376-565-CM26</t>
+          <t>1376-564-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21780,17 +21780,17 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -21799,13 +21799,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2337.71</v>
+        <v>3158.7</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1554-1392-CM26</t>
+          <t>2381-998-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21830,12 +21830,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21845,12 +21845,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -21864,13 +21864,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>859.45</v>
+        <v>1469.65</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2381-998-CM26</t>
+          <t>1554-1392-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21895,12 +21895,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21910,12 +21910,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -21929,7 +21929,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1469.65</v>
+        <v>859.45</v>
       </c>
     </row>
     <row r="335">
@@ -22390,7 +22390,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1376-668-CM26</t>
+          <t>1171166-228-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22415,12 +22415,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22449,13 +22449,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1074.6</v>
+        <v>2586.23</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1171166-228-CM26</t>
+          <t>1376-668-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22480,12 +22480,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22514,7 +22514,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2586.23</v>
+        <v>1074.6</v>
       </c>
     </row>
     <row r="344">
@@ -22975,7 +22975,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1171166-227-CM26</t>
+          <t>1176812-85-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -23034,13 +23034,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>5920.36</v>
+        <v>1085.05</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1176812-81-CM26</t>
+          <t>1171166-227-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -23080,17 +23080,17 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -23099,13 +23099,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2488.2</v>
+        <v>5920.36</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1171166-229-CM26</t>
+          <t>1176812-81-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23145,17 +23145,17 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>8.306.984-8</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -23164,13 +23164,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>3358.31</v>
+        <v>2488.2</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1176812-85-CM26</t>
+          <t>1171166-229-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1085.05</v>
+        <v>3358.31</v>
       </c>
     </row>
     <row r="355">
@@ -23751,7 +23751,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1346283-250-CM26</t>
+          <t>1346283-254-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -23791,12 +23791,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1753.99</v>
+        <v>2932.42</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1346283-254-CM26</t>
+          <t>1346283-250-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2932.42</v>
+        <v>1753.99</v>
       </c>
     </row>
     <row r="365">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -24271,7 +24271,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1176812-92-CM26</t>
+          <t>1171166-239-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24291,7 +24291,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -24311,28 +24311,32 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K371" t="inlineStr"/>
+          <t>8.306.984-8</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1271.92</v>
+        <v>2404.85</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1171166-239-CM26</t>
+          <t>1176812-92-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24352,7 +24356,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -24372,26 +24376,22 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>SONIA ANGÉLICA LOBOS MADRIGAL</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>8.306.984-8</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2404.85</v>
+        <v>1271.92</v>
       </c>
     </row>
     <row r="373">
@@ -25233,6 +25233,71 @@
       </c>
       <c r="M385" s="2" t="n">
         <v>1378.36</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>700-39-CM26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="n">
+        <v>2026.92</v>
       </c>
     </row>
   </sheetData>
